--- a/Mac.xlsx
+++ b/Mac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHubNegar\University2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3290CF-E808-475D-A6E2-EF7841E0B70F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD63677-3E45-4CE5-AE7B-C92DFA297CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="24496" windowHeight="15675" xr2:uid="{C25832E4-7E68-420B-AB58-E9B6C261ECC4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="14">
   <si>
     <t>m3 pro</t>
   </si>
@@ -86,7 +86,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -133,11 +133,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -473,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B732B2B-D1E9-406E-BBF5-9120BAD5D06E}">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.86328125" style="1" bestFit="1" customWidth="1"/>
@@ -481,18 +482,22 @@
     <col min="3" max="3" width="5.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.796875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5.9296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.53125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.796875" style="1"/>
-    <col min="11" max="11" width="15.1328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="6" max="6" width="7.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.53125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.796875" style="1"/>
+    <col min="12" max="12" width="15.1328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.265625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13.86328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.06640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.86328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
@@ -505,26 +510,26 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -540,36 +545,48 @@
       <c r="E2" s="1">
         <v>512</v>
       </c>
-      <c r="F2" s="2">
+      <c r="G2" s="2">
         <v>104000</v>
       </c>
-      <c r="G2" s="2">
+      <c r="H2" s="2">
         <v>1750</v>
       </c>
-      <c r="H2" s="2">
-        <f>F2*G2</f>
+      <c r="I2" s="2">
+        <f t="shared" ref="I2:I7" si="0">G2*H2</f>
         <v>182000000</v>
       </c>
-      <c r="I2" s="2">
-        <v>60000</v>
-      </c>
       <c r="J2" s="2">
-        <f>H2/I2</f>
-        <v>3033.3333333333335</v>
+        <v>59500</v>
       </c>
       <c r="K2" s="2">
+        <f>I2/J2</f>
+        <v>3058.8235294117649</v>
+      </c>
+      <c r="L2" s="2">
         <v>135000000</v>
       </c>
-      <c r="L2" s="2">
-        <f>K2/I2</f>
-        <v>2250</v>
-      </c>
       <c r="M2" s="2">
-        <f t="shared" ref="M2:M3" si="0">K2/G2</f>
+        <f>L2/J2</f>
+        <v>2268.90756302521</v>
+      </c>
+      <c r="N2" s="2">
+        <f>K2-M2</f>
+        <v>789.91596638655483</v>
+      </c>
+      <c r="O2" s="2">
+        <f t="shared" ref="O2:O3" si="1">L2/H2</f>
         <v>77142.857142857145</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="P2" s="3">
+        <f>G2-O2</f>
+        <v>26857.142857142855</v>
+      </c>
+      <c r="Q2" s="2">
+        <f>P2*H2</f>
+        <v>47000000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -585,37 +602,50 @@
       <c r="E3" s="1">
         <v>512</v>
       </c>
-      <c r="F3" s="2">
+      <c r="G3" s="2">
         <v>120000</v>
       </c>
-      <c r="G3" s="2">
-        <f>G2</f>
+      <c r="H3" s="2">
+        <f>H2</f>
         <v>1750</v>
       </c>
-      <c r="H3" s="2">
-        <f>F3*G3</f>
+      <c r="I3" s="2">
+        <f t="shared" si="0"/>
         <v>210000000</v>
       </c>
-      <c r="I3" s="2">
-        <v>60000</v>
-      </c>
       <c r="J3" s="2">
-        <f t="shared" ref="J3:J9" si="1">H3/I3</f>
-        <v>3500</v>
+        <f>J2</f>
+        <v>59500</v>
       </c>
       <c r="K3" s="2">
+        <f t="shared" ref="K3:K9" si="2">I3/J3</f>
+        <v>3529.4117647058824</v>
+      </c>
+      <c r="L3" s="2">
         <v>135000000</v>
       </c>
-      <c r="L3" s="2">
-        <f t="shared" ref="L3:L9" si="2">K3/I3</f>
-        <v>2250</v>
-      </c>
       <c r="M3" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="M3:M9" si="3">L3/J3</f>
+        <v>2268.90756302521</v>
+      </c>
+      <c r="N3" s="2">
+        <f t="shared" ref="N3:N15" si="4">K3-M3</f>
+        <v>1260.5042016806724</v>
+      </c>
+      <c r="O3" s="2">
+        <f t="shared" si="1"/>
         <v>77142.857142857145</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="P3" s="3">
+        <f t="shared" ref="P3:P9" si="5">G3-O3</f>
+        <v>42857.142857142855</v>
+      </c>
+      <c r="Q3" s="2">
+        <f t="shared" ref="Q3:Q9" si="6">P3*H3</f>
+        <v>75000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -631,37 +661,50 @@
       <c r="E4" s="1">
         <v>1000</v>
       </c>
-      <c r="F4" s="3">
+      <c r="G4" s="3">
         <v>144000</v>
       </c>
-      <c r="G4" s="2">
-        <f>G3</f>
+      <c r="H4" s="2">
+        <f>H3</f>
         <v>1750</v>
       </c>
-      <c r="H4" s="2">
-        <f>F4*G4</f>
+      <c r="I4" s="2">
+        <f t="shared" si="0"/>
         <v>252000000</v>
       </c>
-      <c r="I4" s="2">
-        <v>60000</v>
-      </c>
       <c r="J4" s="2">
-        <f t="shared" si="1"/>
-        <v>4200</v>
+        <f t="shared" ref="J4:J14" si="7">J3</f>
+        <v>59500</v>
       </c>
       <c r="K4" s="2">
+        <f t="shared" si="2"/>
+        <v>4235.2941176470586</v>
+      </c>
+      <c r="L4" s="2">
         <v>185000000</v>
       </c>
-      <c r="L4" s="2">
-        <f t="shared" si="2"/>
-        <v>3083.3333333333335</v>
-      </c>
       <c r="M4" s="2">
-        <f>K4/G4</f>
+        <f t="shared" si="3"/>
+        <v>3109.2436974789916</v>
+      </c>
+      <c r="N4" s="2">
+        <f t="shared" si="4"/>
+        <v>1126.0504201680669</v>
+      </c>
+      <c r="O4" s="2">
+        <f>L4/H4</f>
         <v>105714.28571428571</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="P4" s="3">
+        <f t="shared" si="5"/>
+        <v>38285.71428571429</v>
+      </c>
+      <c r="Q4" s="2">
+        <f t="shared" si="6"/>
+        <v>67000000.000000007</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -677,37 +720,50 @@
       <c r="E5" s="1">
         <v>1000</v>
       </c>
-      <c r="F5" s="3">
+      <c r="G5" s="3">
         <v>144000</v>
       </c>
-      <c r="G5" s="2">
-        <f>G4</f>
+      <c r="H5" s="2">
+        <f>H4</f>
         <v>1750</v>
       </c>
-      <c r="H5" s="2">
-        <f>F5*G5</f>
+      <c r="I5" s="2">
+        <f t="shared" si="0"/>
         <v>252000000</v>
       </c>
-      <c r="I5" s="2">
-        <v>60000</v>
-      </c>
       <c r="J5" s="2">
-        <f t="shared" ref="J5" si="3">H5/I5</f>
-        <v>4200</v>
+        <f t="shared" si="7"/>
+        <v>59500</v>
       </c>
       <c r="K5" s="2">
+        <f t="shared" ref="K5" si="8">I5/J5</f>
+        <v>4235.2941176470586</v>
+      </c>
+      <c r="L5" s="2">
         <v>218000000</v>
       </c>
-      <c r="L5" s="2">
-        <f t="shared" ref="L5" si="4">K5/I5</f>
-        <v>3633.3333333333335</v>
-      </c>
       <c r="M5" s="2">
-        <f>K5/G5</f>
+        <f t="shared" ref="M5" si="9">L5/J5</f>
+        <v>3663.8655462184875</v>
+      </c>
+      <c r="N5" s="2">
+        <f t="shared" si="4"/>
+        <v>571.4285714285711</v>
+      </c>
+      <c r="O5" s="2">
+        <f>L5/H5</f>
         <v>124571.42857142857</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="P5" s="3">
+        <f t="shared" si="5"/>
+        <v>19428.571428571435</v>
+      </c>
+      <c r="Q5" s="2">
+        <f t="shared" si="6"/>
+        <v>34000000.000000007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -723,37 +779,50 @@
       <c r="E6" s="1">
         <v>1000</v>
       </c>
-      <c r="F6" s="3">
+      <c r="G6" s="3">
         <v>162000</v>
       </c>
-      <c r="G6" s="2">
-        <f>G5</f>
+      <c r="H6" s="2">
+        <f>H5</f>
         <v>1750</v>
       </c>
-      <c r="H6" s="2">
-        <f>F6*G6</f>
+      <c r="I6" s="2">
+        <f t="shared" si="0"/>
         <v>283500000</v>
       </c>
-      <c r="I6" s="2">
-        <v>60000</v>
-      </c>
       <c r="J6" s="2">
-        <f t="shared" ref="J6" si="5">H6/I6</f>
-        <v>4725</v>
+        <f t="shared" si="7"/>
+        <v>59500</v>
       </c>
       <c r="K6" s="2">
+        <f t="shared" ref="K6" si="10">I6/J6</f>
+        <v>4764.7058823529414</v>
+      </c>
+      <c r="L6" s="2">
         <v>218000000</v>
       </c>
-      <c r="L6" s="2">
-        <f t="shared" ref="L6" si="6">K6/I6</f>
-        <v>3633.3333333333335</v>
-      </c>
       <c r="M6" s="2">
-        <f>K6/G6</f>
+        <f t="shared" ref="M6" si="11">L6/J6</f>
+        <v>3663.8655462184875</v>
+      </c>
+      <c r="N6" s="2">
+        <f t="shared" si="4"/>
+        <v>1100.840336134454</v>
+      </c>
+      <c r="O6" s="2">
+        <f>L6/H6</f>
         <v>124571.42857142857</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="P6" s="3">
+        <f t="shared" si="5"/>
+        <v>37428.571428571435</v>
+      </c>
+      <c r="Q6" s="2">
+        <f t="shared" si="6"/>
+        <v>65500000.000000007</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -769,35 +838,50 @@
       <c r="E7" s="1">
         <v>256</v>
       </c>
-      <c r="F7" s="3">
-        <v>56000</v>
-      </c>
-      <c r="G7" s="2">
-        <f>G4</f>
+      <c r="G7" s="3">
+        <v>55000</v>
+      </c>
+      <c r="H7" s="2">
+        <f>H4</f>
         <v>1750</v>
       </c>
-      <c r="H7" s="2">
-        <f>F7*G7</f>
-        <v>98000000</v>
-      </c>
       <c r="I7" s="2">
-        <v>60000</v>
+        <f t="shared" si="0"/>
+        <v>96250000</v>
       </c>
       <c r="J7" s="2">
-        <f t="shared" si="1"/>
-        <v>1633.3333333333333</v>
-      </c>
-      <c r="K7" s="2"/>
+        <f t="shared" si="7"/>
+        <v>59500</v>
+      </c>
+      <c r="K7" s="2">
+        <f t="shared" si="2"/>
+        <v>1617.6470588235295</v>
+      </c>
       <c r="L7" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>73000000</v>
       </c>
       <c r="M7" s="2">
-        <f t="shared" ref="M7:M9" si="7">K7/G7</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="3"/>
+        <v>1226.8907563025209</v>
+      </c>
+      <c r="N7" s="2">
+        <f t="shared" si="4"/>
+        <v>390.75630252100859</v>
+      </c>
+      <c r="O7" s="2">
+        <f t="shared" ref="O7:O9" si="12">L7/H7</f>
+        <v>41714.285714285717</v>
+      </c>
+      <c r="P7" s="3">
+        <f t="shared" si="5"/>
+        <v>13285.714285714283</v>
+      </c>
+      <c r="Q7" s="2">
+        <f t="shared" si="6"/>
+        <v>23249999.999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -813,35 +897,48 @@
       <c r="E8" s="1">
         <v>512</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>64000</v>
       </c>
-      <c r="G8" s="2">
-        <f t="shared" ref="G8:G9" si="8">G7</f>
+      <c r="H8" s="2">
+        <f t="shared" ref="H8:H12" si="13">H7</f>
         <v>1750</v>
       </c>
-      <c r="H8" s="2">
-        <f t="shared" ref="H8:H9" si="9">F8*G8</f>
+      <c r="I8" s="2">
+        <f t="shared" ref="I8:I9" si="14">G8*H8</f>
         <v>112000000</v>
       </c>
-      <c r="I8" s="2">
-        <v>60000</v>
-      </c>
       <c r="J8" s="2">
-        <f t="shared" si="1"/>
-        <v>1866.6666666666667</v>
-      </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2">
+        <f t="shared" si="7"/>
+        <v>59500</v>
+      </c>
+      <c r="K8" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+        <v>1882.3529411764705</v>
+      </c>
+      <c r="L8" s="2"/>
       <c r="M8" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N8" s="2">
+        <f t="shared" si="4"/>
+        <v>1882.3529411764705</v>
+      </c>
+      <c r="O8" s="2">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
+        <f t="shared" si="5"/>
+        <v>64000</v>
+      </c>
+      <c r="Q8" s="2">
+        <f t="shared" si="6"/>
+        <v>112000000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -857,31 +954,364 @@
       <c r="E9" s="1">
         <v>512</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>72000</v>
       </c>
-      <c r="G9" s="2">
-        <f t="shared" si="8"/>
+      <c r="H9" s="2">
+        <f t="shared" si="13"/>
         <v>1750</v>
       </c>
-      <c r="H9" s="2">
-        <f t="shared" si="9"/>
+      <c r="I9" s="2">
+        <f t="shared" si="14"/>
         <v>126000000</v>
       </c>
-      <c r="I9" s="2">
-        <v>60000</v>
-      </c>
       <c r="J9" s="2">
-        <f t="shared" si="1"/>
-        <v>2100</v>
+        <f t="shared" si="7"/>
+        <v>59500</v>
+      </c>
+      <c r="K9" s="2">
+        <f t="shared" si="2"/>
+        <v>2117.6470588235293</v>
       </c>
       <c r="L9" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>95000000</v>
       </c>
       <c r="M9" s="2">
+        <f t="shared" si="3"/>
+        <v>1596.6386554621849</v>
+      </c>
+      <c r="N9" s="2">
+        <f t="shared" si="4"/>
+        <v>521.00840336134434</v>
+      </c>
+      <c r="O9" s="2">
+        <f t="shared" si="12"/>
+        <v>54285.714285714283</v>
+      </c>
+      <c r="P9" s="3">
+        <f t="shared" si="5"/>
+        <v>17714.285714285717</v>
+      </c>
+      <c r="Q9" s="2">
+        <f t="shared" si="6"/>
+        <v>31000000.000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1">
+        <v>8</v>
+      </c>
+      <c r="C10" s="1">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1">
+        <v>24</v>
+      </c>
+      <c r="E10" s="1">
+        <v>512</v>
+      </c>
+      <c r="G10" s="3">
+        <v>79000</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="13"/>
+        <v>1750</v>
+      </c>
+      <c r="I10" s="2">
+        <f t="shared" ref="I10" si="15">G10*H10</f>
+        <v>138250000</v>
+      </c>
+      <c r="J10" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>59500</v>
+      </c>
+      <c r="K10" s="2">
+        <f t="shared" ref="K10" si="16">I10/J10</f>
+        <v>2323.5294117647059</v>
+      </c>
+      <c r="L10" s="2">
+        <v>95000000</v>
+      </c>
+      <c r="M10" s="2">
+        <f t="shared" ref="M10" si="17">L10/J10</f>
+        <v>1596.6386554621849</v>
+      </c>
+      <c r="N10" s="2">
+        <f t="shared" si="4"/>
+        <v>726.89075630252091</v>
+      </c>
+      <c r="O10" s="2">
+        <f t="shared" ref="O10" si="18">L10/H10</f>
+        <v>54285.714285714283</v>
+      </c>
+      <c r="P10" s="3">
+        <f t="shared" ref="P10" si="19">G10-O10</f>
+        <v>24714.285714285717</v>
+      </c>
+      <c r="Q10" s="2">
+        <f t="shared" ref="Q10" si="20">P10*H10</f>
+        <v>43250000.000000007</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1">
+        <v>16</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="2">
+        <f>H9</f>
+        <v>1750</v>
+      </c>
+      <c r="I11" s="2">
+        <f t="shared" ref="I11" si="21">G11*H11</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="2">
+        <f t="shared" si="7"/>
+        <v>59500</v>
+      </c>
+      <c r="K11" s="2">
+        <f t="shared" ref="K11" si="22">I11/J11</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="2">
+        <v>127300000</v>
+      </c>
+      <c r="M11" s="2">
+        <f t="shared" ref="M11" si="23">L11/J11</f>
+        <v>2139.4957983193276</v>
+      </c>
+      <c r="N11" s="2">
+        <f t="shared" si="4"/>
+        <v>-2139.4957983193276</v>
+      </c>
+      <c r="O11" s="2">
+        <f t="shared" ref="O11" si="24">L11/H11</f>
+        <v>72742.857142857145</v>
+      </c>
+      <c r="P11" s="3">
+        <f t="shared" ref="P11" si="25">G11-O11</f>
+        <v>-72742.857142857145</v>
+      </c>
+      <c r="Q11" s="2">
+        <f t="shared" ref="Q11" si="26">P11*H11</f>
+        <v>-127300000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="1">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1">
+        <v>10</v>
+      </c>
+      <c r="D12" s="1">
+        <v>16</v>
+      </c>
+      <c r="E12" s="1">
+        <v>256</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="2">
+        <f t="shared" si="13"/>
+        <v>1750</v>
+      </c>
+      <c r="I12" s="2">
+        <f t="shared" ref="I12" si="27">G12*H12</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="2">
+        <f t="shared" si="7"/>
+        <v>59500</v>
+      </c>
+      <c r="K12" s="2">
+        <f t="shared" ref="K12" si="28">I12/J12</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="2">
+        <v>99500000</v>
+      </c>
+      <c r="M12" s="2">
+        <f t="shared" ref="M12" si="29">L12/J12</f>
+        <v>1672.2689075630253</v>
+      </c>
+      <c r="N12" s="2">
+        <f t="shared" si="4"/>
+        <v>-1672.2689075630253</v>
+      </c>
+      <c r="O12" s="2">
+        <f t="shared" ref="O12" si="30">L12/H12</f>
+        <v>56857.142857142855</v>
+      </c>
+      <c r="P12" s="3">
+        <f t="shared" ref="P12" si="31">G12-O12</f>
+        <v>-56857.142857142855</v>
+      </c>
+      <c r="Q12" s="2">
+        <f t="shared" ref="Q12" si="32">P12*H12</f>
+        <v>-99500000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="J13" s="2">
+        <f t="shared" si="7"/>
+        <v>59500</v>
+      </c>
+      <c r="N13" s="2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1">
+        <v>11</v>
+      </c>
+      <c r="C14" s="1">
+        <v>14</v>
+      </c>
+      <c r="D14" s="1">
+        <v>18</v>
+      </c>
+      <c r="E14" s="1">
+        <v>512</v>
+      </c>
+      <c r="F14" s="1">
+        <v>14</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2">
+        <v>1750</v>
+      </c>
+      <c r="I14" s="2">
+        <f t="shared" ref="I14" si="33">G14*H14</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
+        <f t="shared" si="7"/>
+        <v>59500</v>
+      </c>
+      <c r="K14" s="2">
+        <f>I14/J14</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="2">
+        <v>107000000</v>
+      </c>
+      <c r="M14" s="2">
+        <f>L14/J14</f>
+        <v>1798.3193277310925</v>
+      </c>
+      <c r="N14" s="2">
+        <f t="shared" si="4"/>
+        <v>-1798.3193277310925</v>
+      </c>
+      <c r="O14" s="2">
+        <f t="shared" ref="O14" si="34">L14/H14</f>
+        <v>61142.857142857145</v>
+      </c>
+      <c r="P14" s="3">
+        <f>G14-O14</f>
+        <v>-61142.857142857145</v>
+      </c>
+      <c r="Q14" s="2">
+        <f>P14*H14</f>
+        <v>-107000000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="1">
+        <v>12</v>
+      </c>
+      <c r="C15" s="1">
+        <v>19</v>
+      </c>
+      <c r="D15" s="1">
+        <v>15</v>
+      </c>
+      <c r="E15" s="1">
+        <v>512</v>
+      </c>
+      <c r="F15" s="1">
+        <v>15</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2">
+        <v>1750</v>
+      </c>
+      <c r="I15" s="2">
+        <f t="shared" ref="I15" si="35">G15*H15</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
+        <f>J14</f>
+        <v>59500</v>
+      </c>
+      <c r="K15" s="2">
+        <f>I15/J15</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="2">
+        <v>112000000</v>
+      </c>
+      <c r="M15" s="2">
+        <f>L15/J15</f>
+        <v>1882.3529411764705</v>
+      </c>
+      <c r="N15" s="2">
+        <f t="shared" si="4"/>
+        <v>-1882.3529411764705</v>
+      </c>
+      <c r="O15" s="2">
+        <f t="shared" ref="O15" si="36">L15/H15</f>
+        <v>64000</v>
+      </c>
+      <c r="P15" s="3">
+        <f>G15-O15</f>
+        <v>-64000</v>
+      </c>
+      <c r="Q15" s="2">
+        <f>P15*H15</f>
+        <v>-112000000</v>
+      </c>
+    </row>
+    <row r="20" spans="6:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="F20" s="2">
+        <v>5000</v>
+      </c>
+      <c r="G20" s="2">
+        <v>38</v>
+      </c>
+      <c r="H20" s="2">
+        <f>F20*G20</f>
+        <v>190000</v>
+      </c>
+      <c r="I20" s="4">
+        <f>H20/37</f>
+        <v>5135.135135135135</v>
       </c>
     </row>
   </sheetData>
